--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7974266-4DD6-456B-B3D1-529112BF0746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE29A81-A758-4FEF-9D4C-39AC759C7024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -2717,7 +2717,7 @@
         <v>128</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C25" si="1">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
+        <f t="shared" ref="C3:C4" si="1">"- ["&amp;LEFT(B3,LEN(B3)-3)&amp;"]("&amp;A3&amp;"/"&amp;B3&amp;")"</f>
         <v>- [Clickhouse-基础使用教程](Clickhouse/Clickhouse-基础使用教程.md)</v>
       </c>
       <c r="D3" t="str">
@@ -3219,7 +3219,7 @@
     <col min="1" max="1" width="8.921875" customWidth="1"/>
     <col min="2" max="2" width="34.921875" customWidth="1"/>
     <col min="3" max="4" width="14.765625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="62.15234375" customWidth="1"/>
+    <col min="5" max="5" width="56.61328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.45">

--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE29A81-A758-4FEF-9D4C-39AC759C7024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57FAC39-CD9A-423C-ADB1-B1E8CFDE62F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="319">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1131,6 +1131,14 @@
   </si>
   <si>
     <t>1度电，到底能炼出多少Tokens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260601-再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2399,8 +2407,7 @@
   <cols>
     <col min="1" max="1" width="8.61328125" customWidth="1"/>
     <col min="2" max="3" width="30.69140625" customWidth="1"/>
-    <col min="4" max="4" width="24.4609375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.84375" style="5" customWidth="1"/>
+    <col min="4" max="5" width="15" style="5" customWidth="1"/>
     <col min="6" max="6" width="38.4609375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2573,17 +2580,23 @@
       <c r="A11" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="5" t="e">
+      <c r="B11" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E11" s="5" t="e">
+        <v>- [再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点](随笔/20260601-再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点.md)</v>
+      </c>
+      <c r="E11" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F11" t="e">
+        <v>- [再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点](/随笔/20260601-再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点.md)</v>
+      </c>
+      <c r="F11" t="str">
         <f t="shared" ref="F11:F15" si="5">"- ["&amp;C11&amp;"](../../"&amp;A11&amp;"/"&amp;LEFT(B11,LEN(B11)-3)&amp;"/)"</f>
-        <v>#VALUE!</v>
+        <v>- [再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点](../../随笔/20260601-再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点/)</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">

--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57FAC39-CD9A-423C-ADB1-B1E8CFDE62F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD2C9D4-F6F2-4196-B6C2-015EFF6B3B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="838" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="321">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1139,6 +1139,14 @@
   </si>
   <si>
     <t>再见CSDN，再见简书：开源博客 + 大模型，让小白也能拥有理想中的个人博客站点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260605-Python揭秘：北京2026新能源家庭指标，花落谁家？.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Python揭秘：北京2026新能源家庭指标，花落谁家？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1783,7 +1791,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.69140625" customWidth="1"/>
@@ -2017,6 +2025,114 @@
       <c r="F10" t="str">
         <f t="shared" si="0"/>
         <v>- [Python 如何确定K-Means聚类的簇数](../../数据分析与挖掘/Python-如何确定K-Means聚类的簇数/)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" t="s">
+        <v>320</v>
+      </c>
+      <c r="D14" s="5" t="str">
+        <f>"- ["&amp;MID(B14,10,LEN(B14)-12)&amp;"]("&amp;A14&amp;"/"&amp;B14&amp;")"</f>
+        <v>- [Python揭秘：北京2026新能源家庭指标，花落谁家？](数据分析与挖掘/20260605-Python揭秘：北京2026新能源家庭指标，花落谁家？.md)</v>
+      </c>
+      <c r="E14" s="5" t="str">
+        <f>"- ["&amp;MID(B14,10,LEN(B14)-12)&amp;"](/"&amp;A14&amp;"/"&amp;B14&amp;")"</f>
+        <v>- [Python揭秘：北京2026新能源家庭指标，花落谁家？](/数据分析与挖掘/20260605-Python揭秘：北京2026新能源家庭指标，花落谁家？.md)</v>
+      </c>
+      <c r="F14" t="str">
+        <f>"- ["&amp;C14&amp;"](../../"&amp;A14&amp;"/"&amp;LEFT(B14,LEN(B14)-3)&amp;"/)"</f>
+        <v>- [Python揭秘：北京2026新能源家庭指标，花落谁家？](../../数据分析与挖掘/20260605-Python揭秘：北京2026新能源家庭指标，花落谁家？/)</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="5" t="e">
+        <f t="shared" ref="D15:D20" si="3">"- ["&amp;MID(B15,10,LEN(B15)-12)&amp;"]("&amp;A15&amp;"/"&amp;B15&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" s="5" t="e">
+        <f t="shared" ref="E15:E20" si="4">"- ["&amp;MID(B15,10,LEN(B15)-12)&amp;"](/"&amp;A15&amp;"/"&amp;B15&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="5" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E16" s="5" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="5" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E17" s="5" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="5" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E18" s="5" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="5" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E19" s="5" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="5" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E20" s="5" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD2C9D4-F6F2-4196-B6C2-015EFF6B3B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DFD59B-3578-4D39-8005-2FD818F7A563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="838" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="323">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1147,6 +1147,14 @@
   </si>
   <si>
     <t>Python揭秘：北京2026新能源家庭指标，花落谁家？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260616-从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2719,17 +2727,23 @@
       <c r="A12" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="5" t="e">
+      <c r="B12" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" t="s">
+        <v>322</v>
+      </c>
+      <c r="D12" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E12" s="5" t="e">
+        <v>- [从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？](随笔/20260616-从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？.md)</v>
+      </c>
+      <c r="E12" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F12" t="e">
+        <v>- [从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？](/随笔/20260616-从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？.md)</v>
+      </c>
+      <c r="F12" t="str">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>- [从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？](../../随笔/20260616-从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？/)</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">

--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DFD59B-3578-4D39-8005-2FD818F7A563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC1B743-0EF8-4A02-A95F-A899632A4041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="325">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1155,6 +1155,14 @@
   </si>
   <si>
     <t>从超平面到分散式表示：传统机器学习与神经网络到底学到了什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260706-回顾协方差含义，利用Python进行计算.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回顾协方差含义，利用Python进行计算</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2396,7 +2404,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.3828125" customWidth="1"/>
@@ -2516,6 +2524,138 @@
       <c r="F5" t="str">
         <f t="shared" si="0"/>
         <v>- [Python利用枚举法，解决一道面试算法题](../../数学知识/Python利用枚举法，解决一道面试算法题/)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D9" s="5" t="str">
+        <f>"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"]("&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+        <v>- [回顾协方差含义，利用Python进行计算](数学知识/20260706-回顾协方差含义，利用Python进行计算.md)</v>
+      </c>
+      <c r="E9" s="5" t="str">
+        <f>"- ["&amp;MID(B9,10,LEN(B9)-12)&amp;"](/"&amp;A9&amp;"/"&amp;B9&amp;")"</f>
+        <v>- [回顾协方差含义，利用Python进行计算](/数学知识/20260706-回顾协方差含义，利用Python进行计算.md)</v>
+      </c>
+      <c r="F9" t="str">
+        <f>"- ["&amp;C9&amp;"](../../"&amp;A9&amp;"/"&amp;LEFT(B9,LEN(B9)-3)&amp;"/)"</f>
+        <v>- [回顾协方差含义，利用Python进行计算](../../数学知识/20260706-回顾协方差含义，利用Python进行计算/)</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="5" t="e">
+        <f t="shared" ref="D10:D15" si="1">"- ["&amp;MID(B10,10,LEN(B10)-12)&amp;"]("&amp;A10&amp;"/"&amp;B10&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E10" s="5" t="e">
+        <f t="shared" ref="E10:E15" si="2">"- ["&amp;MID(B10,10,LEN(B10)-12)&amp;"](/"&amp;A10&amp;"/"&amp;B10&amp;")"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" t="e">
+        <f>"- ["&amp;C10&amp;"](../../"&amp;A10&amp;"/"&amp;LEFT(B10,LEN(B10)-3)&amp;"/)"</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F11" t="e">
+        <f t="shared" ref="F11:F15" si="3">"- ["&amp;C11&amp;"](../../"&amp;A11&amp;"/"&amp;LEFT(B11,LEN(B11)-3)&amp;"/)"</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E12" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F12" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E13" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F13" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F14" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F15" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\datashare-blog\src\content\posts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\project-github\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC1B743-0EF8-4A02-A95F-A899632A4041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57461344-F851-44ED-8D6F-C113AE3E45A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="327">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1163,6 +1163,14 @@
   </si>
   <si>
     <t>回顾协方差含义，利用Python进行计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260727-别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2077,13 +2085,23 @@
       <c r="A15" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="5" t="e">
+      <c r="B15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C15" t="s">
+        <v>326</v>
+      </c>
+      <c r="D15" s="5" t="str">
         <f t="shared" ref="D15:D20" si="3">"- ["&amp;MID(B15,10,LEN(B15)-12)&amp;"]("&amp;A15&amp;"/"&amp;B15&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E15" s="5" t="e">
+        <v>- [别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标](数据分析与挖掘/20260727-别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标.md)</v>
+      </c>
+      <c r="E15" s="5" t="str">
         <f t="shared" ref="E15:E20" si="4">"- ["&amp;MID(B15,10,LEN(B15)-12)&amp;"](/"&amp;A15&amp;"/"&amp;B15&amp;")"</f>
-        <v>#VALUE!</v>
+        <v>- [别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标](/数据分析与挖掘/20260727-别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标.md)</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" ref="F15:F20" si="5">"- ["&amp;C15&amp;"](../../"&amp;A15&amp;"/"&amp;LEFT(B15,LEN(B15)-3)&amp;"/)"</f>
+        <v>- [别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标](../../数据分析与挖掘/20260727-别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标/)</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
@@ -2098,8 +2116,12 @@
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F16" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -2111,8 +2133,12 @@
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F17" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -2124,8 +2150,12 @@
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F18" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -2137,8 +2167,12 @@
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F19" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -2148,6 +2182,10 @@
       </c>
       <c r="E20" s="5" t="e">
         <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F20" t="e">
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/src/content/posts/文章列表.xlsx
+++ b/src/content/posts/文章列表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\个人\project-github\datashare-blog\src\content\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57461344-F851-44ED-8D6F-C113AE3E45A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF09596-3F31-4432-AD01-D6B39E5ECC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="838" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="polars-学习" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="329">
   <si>
     <t>md文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1171,6 +1171,14 @@
   </si>
   <si>
     <t>别被准确率骗了！深入解读 Informedness 与 Markedness 两大稳健评估指标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260902-鸢尾花书系列与矩阵两个视角.md</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸢尾花书系列与矩阵两个视角</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2446,7 +2454,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.3828125" customWidth="1"/>
-    <col min="2" max="2" width="35.3828125" customWidth="1"/>
+    <col min="2" max="2" width="41.765625" customWidth="1"/>
     <col min="3" max="3" width="19.53515625" customWidth="1"/>
     <col min="4" max="5" width="12.15234375" style="5" customWidth="1"/>
     <col min="6" max="6" width="41.3046875" customWidth="1"/>
@@ -2598,17 +2606,23 @@
       <c r="A10" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="5" t="e">
+      <c r="B10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" s="5" t="str">
         <f t="shared" ref="D10:D15" si="1">"- ["&amp;MID(B10,10,LEN(B10)-12)&amp;"]("&amp;A10&amp;"/"&amp;B10&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E10" s="5" t="e">
+        <v>- [鸢尾花书系列与矩阵两个视角](数学知识/20260902-鸢尾花书系列与矩阵两个视角.md)</v>
+      </c>
+      <c r="E10" s="5" t="str">
         <f t="shared" ref="E10:E15" si="2">"- ["&amp;MID(B10,10,LEN(B10)-12)&amp;"](/"&amp;A10&amp;"/"&amp;B10&amp;")"</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F10" t="e">
+        <v>- [鸢尾花书系列与矩阵两个视角](/数学知识/20260902-鸢尾花书系列与矩阵两个视角.md)</v>
+      </c>
+      <c r="F10" t="str">
         <f>"- ["&amp;C10&amp;"](../../"&amp;A10&amp;"/"&amp;LEFT(B10,LEN(B10)-3)&amp;"/)"</f>
-        <v>#VALUE!</v>
+        <v>- [鸢尾花书系列与矩阵两个视角](../../数学知识/20260902-鸢尾花书系列与矩阵两个视角/)</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
